--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC35E693-E847-4B8C-9566-6BA605249080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B56661F-94BE-411E-BFAA-BE01242A6D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3096,14 +3096,6 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" t="s">
-        <v>121</v>
-      </c>
-    </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>164</v>
@@ -3267,11 +3259,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" customWidth="1"/>
-    <col min="2" max="2" width="32.6328125" customWidth="1"/>
+    <col min="1" max="1" width="56.26953125" customWidth="1"/>
+    <col min="2" max="2" width="41.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -3320,6 +3312,14 @@
       </c>
       <c r="B6" s="3" t="s">
         <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B56661F-94BE-411E-BFAA-BE01242A6D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164456BC-EDD3-45A1-91A8-B553D6727E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
     <sheet name="составные важные" sheetId="6" r:id="rId2"/>
-    <sheet name="запятые" sheetId="9" r:id="rId3"/>
-    <sheet name="Вездесущие" sheetId="3" r:id="rId4"/>
-    <sheet name="Неизменные" sheetId="5" r:id="rId5"/>
-    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId6"/>
-    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId7"/>
+    <sheet name="составные_длинные" sheetId="11" r:id="rId3"/>
+    <sheet name="запятые" sheetId="9" r:id="rId4"/>
+    <sheet name="Вездесущие" sheetId="3" r:id="rId5"/>
+    <sheet name="Неизменные" sheetId="5" r:id="rId6"/>
+    <sheet name="Неизменные_короткие" sheetId="8" r:id="rId7"/>
+    <sheet name="Неизменные_длинные" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Неизменные!$A$1:$B$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Неизменные_длинные!$A$1:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Неизменные!$A$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Неизменные_длинные!$A$1:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'составные важные'!$A$1:$B$28</definedName>
   </definedNames>
@@ -3000,14 +3001,6 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>136</v>
@@ -3258,6 +3251,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14319332-0B63-4573-9B96-3A9844A1EE10}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40.54296875" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3327,7 +3342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6986B8E4-10EA-40D7-B7C4-648CE1726987}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3393,7 +3408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
   <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3809,7 +3824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3991,7 +4006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9D2386-1B86-4B4D-9994-D45D2591761D}">
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/словари/si pi 2011.xlsx
+++ b/словари/si pi 2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164456BC-EDD3-45A1-91A8-B553D6727E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6ABCB7-B168-4D22-8785-8F71EF661935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Неизменные!$A$1:$B$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Неизменные_длинные!$A$1:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные!$A$1:$B$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'составные важные'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'составные важные'!$A$1:$B$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2000,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" customWidth="1"/>
@@ -2008,913 +2008,897 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" t="s">
-        <v>131</v>
+      <c r="A1" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>473</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>171</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>166</v>
+        <v>477</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>167</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>244</v>
+        <v>359</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>245</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>242</v>
+        <v>361</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>243</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>302</v>
+        <v>409</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>303</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" t="s">
-        <v>107</v>
+        <v>170</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" t="s">
-        <v>119</v>
+      <c r="A10" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>313</v>
+        <v>423</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>314</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>320</v>
+        <v>417</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>321</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>156</v>
+        <v>399</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>157</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>144</v>
+      <c r="A14" s="3" t="s">
+        <v>465</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>145</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>294</v>
+        <v>479</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>295</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>283</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>333</v>
+        <v>454</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>334</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
+      <c r="A20" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>247</v>
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>259</v>
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>261</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>250</v>
+        <v>377</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>251</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>248</v>
+        <v>375</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>249</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>252</v>
+        <v>379</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>253</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>254</v>
+        <v>421</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>257</v>
+        <v>467</v>
+      </c>
+      <c r="B29" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
+      <c r="A30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>322</v>
+        <v>424</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>323</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>132</v>
-      </c>
-      <c r="B32" t="s">
-        <v>133</v>
+      <c r="A32" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>238</v>
+      <c r="A33" t="s">
+        <v>144</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>239</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>292</v>
+        <v>437</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>293</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>174</v>
+        <v>337</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>175</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>177</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>286</v>
+        <v>393</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>287</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>291</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>266</v>
+        <v>441</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>267</v>
+        <v>442</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>265</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>272</v>
+        <v>433</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>273</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>280</v>
+        <v>435</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>281</v>
+        <v>436</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>270</v>
+        <v>492</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>271</v>
+        <v>493</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>278</v>
+        <v>432</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>279</v>
+        <v>445</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>274</v>
+        <v>370</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>275</v>
+        <v>371</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>276</v>
+        <v>401</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>277</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>268</v>
+        <v>333</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>269</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>219</v>
+        <v>439</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>316</v>
+      <c r="A50" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>296</v>
+        <v>387</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>297</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" t="s">
-        <v>350</v>
+      <c r="A52" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>154</v>
-      </c>
-      <c r="B53" t="s">
-        <v>155</v>
+      <c r="A53" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54" t="s">
-        <v>69</v>
+      <c r="A54" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>306</v>
-      </c>
-      <c r="B55" t="s">
-        <v>327</v>
+      <c r="A55" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>325</v>
+        <v>262</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>326</v>
+        <v>263</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>329</v>
+        <v>260</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>305</v>
-      </c>
-      <c r="B58" t="s">
-        <v>328</v>
+      <c r="A58" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>337</v>
+        <v>248</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>338</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B60" t="s">
-        <v>340</v>
+        <v>252</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>345</v>
+        <v>254</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>346</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>361</v>
+        <v>322</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>362</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>364</v>
+      <c r="A64" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>370</v>
+        <v>238</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>371</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>373</v>
+        <v>292</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>374</v>
+        <v>293</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>375</v>
+        <v>458</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>376</v>
+        <v>459</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
-        <v>377</v>
+        <v>174</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>378</v>
+        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>379</v>
+        <v>176</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>380</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>384</v>
+        <v>287</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
-        <v>385</v>
+        <v>216</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
-        <v>389</v>
+        <v>290</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>390</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
-        <v>391</v>
+        <v>266</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>392</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
-        <v>393</v>
+        <v>264</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>394</v>
+        <v>265</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>398</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
-        <v>399</v>
+        <v>280</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>400</v>
+        <v>281</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
-        <v>401</v>
+        <v>270</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>402</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
-        <v>403</v>
+        <v>278</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>404</v>
+        <v>279</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
-        <v>405</v>
+        <v>274</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>406</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
-        <v>407</v>
+        <v>276</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>408</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
-        <v>409</v>
+        <v>268</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>410</v>
+        <v>269</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
-        <v>411</v>
+        <v>507</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>412</v>
+        <v>508</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>416</v>
+        <v>218</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
-        <v>419</v>
+        <v>315</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>420</v>
+        <v>316</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>418</v>
+        <v>297</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>425</v>
+      <c r="A91" t="s">
+        <v>63</v>
+      </c>
+      <c r="B91" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
-        <v>432</v>
+        <v>345</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>445</v>
+        <v>346</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
-        <v>437</v>
+        <v>501</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>438</v>
+        <v>502</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
-        <v>441</v>
+        <v>403</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>442</v>
+        <v>404</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>444</v>
+        <v>498</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>459</v>
+      <c r="A101" t="s">
+        <v>154</v>
+      </c>
+      <c r="B101" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>498</v>
+      <c r="A102" t="s">
+        <v>68</v>
+      </c>
+      <c r="B102" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
-        <v>461</v>
+        <v>381</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>462</v>
+        <v>382</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
-        <v>465</v>
+        <v>363</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>466</v>
+        <v>364</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="B105" t="s">
-        <v>468</v>
+        <v>365</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>502</v>
+      <c r="A106" t="s">
+        <v>306</v>
+      </c>
+      <c r="B106" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
-        <v>473</v>
+        <v>325</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>474</v>
+        <v>326</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>478</v>
+        <v>217</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>480</v>
+      <c r="A109" t="s">
+        <v>305</v>
+      </c>
+      <c r="B109" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>484</v>
+        <v>339</v>
+      </c>
+      <c r="B110" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B112" s="3" t="s">
         <v>497</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>508</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B109" xr:uid="{8324EBA4-4FF9-4984-A3D6-56F6E9ADC9D8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B108">
-    <sortCondition ref="A1:A108"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B113">
+    <sortCondition ref="A1:A113"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2922,7 +2906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.453125" customWidth="1"/>
@@ -2962,67 +2946,75 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>168</v>
+      <c r="A5" s="13" t="s">
+        <v>319</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>319</v>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>355</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" t="s">
-        <v>149</v>
-      </c>
-    </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>141</v>
+      <c r="A9" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" t="s">
-        <v>137</v>
+      <c r="A11" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>152</v>
-      </c>
-      <c r="B13" t="s">
-        <v>153</v>
+        <v>140</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -3051,90 +3043,98 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>114</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>74</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>165</v>
+      <c r="A23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" t="s">
-        <v>129</v>
+      <c r="A24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>159</v>
+        <v>494</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>324</v>
+        <v>367</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28" t="s">
-        <v>139</v>
+      <c r="A28" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -3155,96 +3155,24 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>353</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>179</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>510</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B28" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B34">
-    <sortCondition ref="A2:A34"/>
+  <autoFilter ref="A1:B27" xr:uid="{31F0911E-798C-4521-82CD-5859C5910073}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B40">
+    <sortCondition ref="A2:A40"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3252,7 +3180,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14319332-0B63-4573-9B96-3A9844A1EE10}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.54296875" customWidth="1"/>
@@ -3267,6 +3195,70 @@
         <v>309</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3274,7 +3266,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9ACB0-12B1-45DA-8517-08CD2F731837}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.26953125" customWidth="1"/>
@@ -3335,6 +3327,14 @@
       </c>
       <c r="B7" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -3410,7 +3410,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF1C28C-88BD-4D4A-9553-B355224DEC0C}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.36328125" customWidth="1"/>
@@ -3780,41 +3780,33 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>369</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s">
-        <v>372</v>
+        <v>457</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="B49" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>482</v>
-      </c>
-      <c r="B50" t="s">
         <v>481</v>
       </c>
     </row>
@@ -3826,7 +3818,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571ED9EF-5F43-4519-9255-E9A74F7B803C}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3999,6 +3991,14 @@
       </c>
       <c r="B21" t="s">
         <v>505</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>341</v>
+      </c>
+      <c r="B22" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
